--- a/education_forms/044_special_education_admission_form--education_forms.xlsx
+++ b/education_forms/044_special_education_admission_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Student Additional Info Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>student_signature</t>
+          <t>student_signature_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date Signed</t>
+          <t>Parent Signature Date</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Parent Info Additional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Student Program Info Other</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1240,8 +1240,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general_education_diploma'}</t>
+          <t>general_education_diploma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General Education Diploma'}</t>
+          <t>General Education Diploma</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'career_and_technical_education'}</t>
+          <t>career_and_technical_education</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Career and Technical Education'}</t>
+          <t>Career and Technical Education</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'special_education_diploma'}</t>
+          <t>special_education_diploma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Special Education Diploma'}</t>
+          <t>Special Education Diploma</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'guardian'}</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Guardian'}</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'relative'}</t>
+          <t>relative</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Relative'}</t>
+          <t>Relative</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'elementary_school'}</t>
+          <t>elementary_school</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Elementary School'}</t>
+          <t>Elementary School</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High School Diploma'}</t>
+          <t>High School Diploma</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'some_high_school'}</t>
+          <t>some_high_school</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Some High School'}</t>
+          <t>Some High School</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'college_diploma'}</t>
+          <t>college_diploma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'College Diploma'}</t>
+          <t>College Diploma</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'special_diploma'}</t>
+          <t>special_diploma</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Special Diploma'}</t>
+          <t>Special Diploma</t>
         </is>
       </c>
     </row>
